--- a/dados/ambev-revenda.xlsx
+++ b/dados/ambev-revenda.xlsx
@@ -1,34 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEMARCO.TALLISON\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{08AD4BA1-7C68-4780-AD75-9E04B616A612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+  <si>
+    <t>Identificador</t>
+  </si>
+  <si>
+    <t>Observação</t>
+  </si>
+  <si>
+    <t>Data Validação</t>
+  </si>
+  <si>
+    <t>Motivo</t>
+  </si>
+  <si>
+    <t>GGC0B68</t>
+  </si>
+  <si>
+    <t>BCX4B18</t>
+  </si>
+  <si>
+    <t>DBL4H23</t>
+  </si>
+  <si>
+    <t>BCX7H22</t>
+  </si>
+  <si>
+    <t>UJX1F39</t>
+  </si>
+  <si>
+    <t>POX8094</t>
+  </si>
+  <si>
+    <t>MWF1H91</t>
+  </si>
+  <si>
+    <t>TYD6B38</t>
+  </si>
+  <si>
+    <t>UMM4I85</t>
+  </si>
+  <si>
+    <t>QKI4A01</t>
+  </si>
+  <si>
+    <t>EZZ2C93</t>
+  </si>
+  <si>
+    <t>ANP2J95</t>
+  </si>
+  <si>
+    <t>POJ3867</t>
+  </si>
+  <si>
+    <t>TTA2E39</t>
+  </si>
+  <si>
+    <t>MLV4E58</t>
+  </si>
+  <si>
+    <t>RVC0I25</t>
+  </si>
+  <si>
+    <t>EQW2G22</t>
+  </si>
+  <si>
+    <t>KDL8G91</t>
+  </si>
+  <si>
+    <t>PCV1H90</t>
+  </si>
+  <si>
+    <t>PCT9F41</t>
+  </si>
+  <si>
+    <t>UPG5I59</t>
+  </si>
+  <si>
+    <t>UKN6D51</t>
+  </si>
+  <si>
+    <t>RAS3D08</t>
+  </si>
+  <si>
+    <t>QJK2584</t>
+  </si>
+  <si>
+    <t>SZF9D49</t>
+  </si>
+  <si>
+    <t>EOE5D76</t>
+  </si>
+  <si>
+    <t>RYX1B24</t>
+  </si>
+  <si>
+    <t>TFZ7G76</t>
+  </si>
+  <si>
+    <t>TFN4H68</t>
+  </si>
+  <si>
+    <t>HSI0E47</t>
+  </si>
+  <si>
+    <t>RPF6E59</t>
+  </si>
+  <si>
+    <t>RXF1C23</t>
+  </si>
+  <si>
+    <t>POY5761</t>
+  </si>
+  <si>
+    <t>RYO8C03</t>
+  </si>
+  <si>
+    <t>SXY6E90</t>
+  </si>
+  <si>
+    <t>TSV9D13</t>
+  </si>
+  <si>
+    <t>Lateral</t>
+  </si>
+  <si>
+    <t>IA: A imagem não mostra a lateral completa do veículo, pois a parte traseira do implemento (carreta) está cortada.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral_veiculo não mostra a lateral completa do veículo, apresentando cortes na parte frontal da cabine</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral apresenta um corte na parte frontal do veículo, impedindo a visualização completa da lateral.</t>
+  </si>
+  <si>
+    <t>IA: A imagem lateral não mostra o veículo por completo, apresentando corte na parte traseira do implemento.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +190,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,40 +494,340 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="4" max="4" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Identificador</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Observação</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Data Validação</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Motivo</t>
-        </is>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>46314.401818599537</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46314.562868692126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46314.563114722223</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46314.563403969907</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46314.69769134259</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46315.318822766203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46315.317889062499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46315.31746972222</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46315.438615324078</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46315.438895590276</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46315.593651215277</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46315.593879236112</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46315.57955480324</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46315.615193576392</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46315.680130868059</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46315.68035584491</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46316.39089962963</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46316.419015405096</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46316.487592604164</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46316.450397430555</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46316.450747453702</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46316.488185856484</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46316.487865011572</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46316.535440231484</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46316.535663043978</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46316.535913796295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46316.652274456021</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46316.685385324075</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46316.7138040625</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46317.186600416666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46317.336052175924</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46317.432928125003</v>
+      </c>
+      <c r="D33" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46317.55757005787</v>
+      </c>
+      <c r="D34" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46317.677610775463</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46318.184340243053</v>
+      </c>
+      <c r="D36" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46318.184671805553</v>
       </c>
     </row>
   </sheetData>

--- a/dados/ambev-revenda.xlsx
+++ b/dados/ambev-revenda.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEMARCO.TALLISON\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{08AD4BA1-7C68-4780-AD75-9E04B616A612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD35B3A6-388D-4F1F-91ED-9324D2AEF704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Base" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Base!$A$1:$D$45</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>Identificador</t>
   </si>
@@ -155,6 +158,33 @@
   </si>
   <si>
     <t>IA: A imagem lateral não mostra o veículo por completo, apresentando corte na parte traseira do implemento.</t>
+  </si>
+  <si>
+    <t>JYP6I86</t>
+  </si>
+  <si>
+    <t>RID7G25</t>
+  </si>
+  <si>
+    <t>RIK5A24</t>
+  </si>
+  <si>
+    <t>POL3816</t>
+  </si>
+  <si>
+    <t>NML6060</t>
+  </si>
+  <si>
+    <t>OIA9812</t>
+  </si>
+  <si>
+    <t>RLX5A70</t>
+  </si>
+  <si>
+    <t>Pendente Frente e Lateral</t>
+  </si>
+  <si>
+    <t>- Lateral</t>
   </si>
 </sst>
 </file>
@@ -495,7 +525,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D37"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -518,7 +549,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -526,7 +557,7 @@
         <v>46314.401818599537</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -534,7 +565,7 @@
         <v>46314.562868692126</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -542,7 +573,7 @@
         <v>46314.563114722223</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -564,7 +595,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -572,7 +603,7 @@
         <v>46315.318822766203</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -580,7 +611,7 @@
         <v>46315.317889062499</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -588,7 +619,7 @@
         <v>46315.31746972222</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -596,7 +627,7 @@
         <v>46315.438615324078</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -604,7 +635,7 @@
         <v>46315.438895590276</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -612,7 +643,7 @@
         <v>46315.593651215277</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -620,7 +651,7 @@
         <v>46315.593879236112</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -628,7 +659,7 @@
         <v>46315.57955480324</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -636,7 +667,7 @@
         <v>46315.615193576392</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -644,7 +675,7 @@
         <v>46315.680130868059</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -652,7 +683,7 @@
         <v>46315.68035584491</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -660,7 +691,7 @@
         <v>46316.39089962963</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -668,7 +699,7 @@
         <v>46316.419015405096</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -676,7 +707,7 @@
         <v>46316.487592604164</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -684,7 +715,7 @@
         <v>46316.450397430555</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -692,7 +723,7 @@
         <v>46316.450747453702</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -700,7 +731,7 @@
         <v>46316.488185856484</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -708,7 +739,7 @@
         <v>46316.487865011572</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -716,7 +747,7 @@
         <v>46316.535440231484</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -724,7 +755,7 @@
         <v>46316.535663043978</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -732,7 +763,7 @@
         <v>46316.535913796295</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -740,7 +771,7 @@
         <v>46316.652274456021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -748,7 +779,7 @@
         <v>46316.685385324075</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -756,7 +787,7 @@
         <v>46316.7138040625</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -764,7 +795,7 @@
         <v>46317.186600416666</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -800,7 +831,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -822,7 +853,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -830,7 +861,87 @@
         <v>46318.184671805553</v>
       </c>
     </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46318.497205798609</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46318.497460995372</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s">
+        <v>52</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46318.497898379632</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46318.498176250003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46318.496051875001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46318.550326504628</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>51</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46318.549818946762</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46318.550026747682</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D45" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dados/ambev-revenda.xlsx
+++ b/dados/ambev-revenda.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DEMARCO.TALLISON\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupodemarco-my.sharepoint.com/personal/tallison_jesus_demarco_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD35B3A6-388D-4F1F-91ED-9324D2AEF704}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{386103A3-67FF-4E61-9D3A-AF0A07A8DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B947A203-95E2-4BD6-9652-24C620998008}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>Identificador</t>
   </si>
@@ -185,6 +185,12 @@
   </si>
   <si>
     <t>- Lateral</t>
+  </si>
+  <si>
+    <t>IA: A lateral do veículo não está totalmente visível, pois a parte traseira do implemento está cortada na imagem.</t>
+  </si>
+  <si>
+    <t>IA: A imagem não mostra a lateral completa do veículo, pois a parte traseira da carroceria está cortada na lateral esquerda da foto.</t>
   </si>
 </sst>
 </file>
@@ -525,7 +531,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -549,7 +554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -557,7 +562,7 @@
         <v>46314.401818599537</v>
       </c>
     </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -565,7 +570,7 @@
         <v>46314.562868692126</v>
       </c>
     </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -573,7 +578,7 @@
         <v>46314.563114722223</v>
       </c>
     </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -595,7 +600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -603,7 +608,7 @@
         <v>46315.318822766203</v>
       </c>
     </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -611,7 +616,7 @@
         <v>46315.317889062499</v>
       </c>
     </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -619,7 +624,7 @@
         <v>46315.31746972222</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -627,7 +632,7 @@
         <v>46315.438615324078</v>
       </c>
     </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -635,7 +640,7 @@
         <v>46315.438895590276</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -643,7 +648,7 @@
         <v>46315.593651215277</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -651,7 +656,7 @@
         <v>46315.593879236112</v>
       </c>
     </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -659,7 +664,7 @@
         <v>46315.57955480324</v>
       </c>
     </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -667,7 +672,7 @@
         <v>46315.615193576392</v>
       </c>
     </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -675,7 +680,7 @@
         <v>46315.680130868059</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -683,7 +688,7 @@
         <v>46315.68035584491</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -691,7 +696,7 @@
         <v>46316.39089962963</v>
       </c>
     </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -699,7 +704,7 @@
         <v>46316.419015405096</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -707,7 +712,7 @@
         <v>46316.487592604164</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -715,7 +720,7 @@
         <v>46316.450397430555</v>
       </c>
     </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -723,7 +728,7 @@
         <v>46316.450747453702</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -731,7 +736,7 @@
         <v>46316.488185856484</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -739,7 +744,7 @@
         <v>46316.487865011572</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -747,7 +752,7 @@
         <v>46316.535440231484</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -755,7 +760,7 @@
         <v>46316.535663043978</v>
       </c>
     </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -763,7 +768,7 @@
         <v>46316.535913796295</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -771,7 +776,7 @@
         <v>46316.652274456021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -779,7 +784,7 @@
         <v>46316.685385324075</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -787,7 +792,7 @@
         <v>46316.7138040625</v>
       </c>
     </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -795,7 +800,7 @@
         <v>46317.186600416666</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -831,7 +836,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -853,7 +858,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -871,8 +876,11 @@
       <c r="C38" s="1">
         <v>46318.497205798609</v>
       </c>
-    </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D38" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -891,7 +899,7 @@
         <v>46318.497898379632</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -899,7 +907,7 @@
         <v>46318.498176250003</v>
       </c>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -917,8 +925,11 @@
       <c r="C43" s="1">
         <v>46318.550326504628</v>
       </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="D43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -926,7 +937,7 @@
         <v>46318.549818946762</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" t="s">
         <v>50</v>
       </c>
@@ -935,13 +946,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D45" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:D45" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{96a13d59-91c6-41b6-a5fa-a0e17fd4925a}" enabled="0" method="" siteId="{96a13d59-91c6-41b6-a5fa-a0e17fd4925a}" removed="1"/>
+</clbl:labelList>
 </file>
--- a/dados/ambev-revenda.xlsx
+++ b/dados/ambev-revenda.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupodemarco-my.sharepoint.com/personal/tallison_jesus_demarco_com_br/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{386103A3-67FF-4E61-9D3A-AF0A07A8DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B947A203-95E2-4BD6-9652-24C620998008}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{386103A3-67FF-4E61-9D3A-AF0A07A8DBAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0BBD5E-36A0-48EA-BD88-2770A7B63BFB}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -181,9 +181,6 @@
     <t>RLX5A70</t>
   </si>
   <si>
-    <t>Pendente Frente e Lateral</t>
-  </si>
-  <si>
     <t>- Lateral</t>
   </si>
   <si>
@@ -191,6 +188,9 @@
   </si>
   <si>
     <t>IA: A imagem não mostra a lateral completa do veículo, pois a parte traseira da carroceria está cortada na lateral esquerda da foto.</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
 </sst>
 </file>
@@ -877,7 +877,7 @@
         <v>46318.497205798609</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
@@ -893,7 +893,7 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C40" s="1">
         <v>46318.497898379632</v>
@@ -920,13 +920,13 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="1">
         <v>46318.550326504628</v>
       </c>
       <c r="D43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
